--- a/stories/arbres/TREE-JEU-001.xlsx
+++ b/stories/arbres/TREE-JEU-001.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Adam est près de la fenêtre, avec papa. Un ballon souple est là. Papa dit : on se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu, le tapis. Adam passe le ballon à papa. Papa attend, puis passe. Tour. Espace du jeu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
+          <t>Adam est près de la fenêtre, avec papa. Un ballon souple est là. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu, le tapis. Adam passe le ballon à papa. Papa attend, puis passe. Tour. Espace du jeu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Adam est près de la fenêtre, avec papa. Un ballon souple est là.
+papa|On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu, le tapis.
+narrateur|Adam passe le ballon à papa. Papa attend, puis passe. Tour. Espace du jeu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1511,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le train, le bus, ou la voiture.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1540,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Adam pose le train à côté. Puis Adam passe le ballon. Tour. Espace du jeu. Papa dit : on passe, on attend. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
+          <t>Adam pose le train à côté. Puis Adam passe le ballon. Tour. Espace du jeu. On passe, on attend. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1678,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose le train à côté. Puis Adam passe le ballon. Tour. Espace du jeu.
+papa|On passe, on attend. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1860,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le ballon, on le fait quoi ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2033,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a passé le ballon. Tour. Espace du jeu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2181,6 +2226,11 @@
       <c r="AV7" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2345,6 +2395,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers Tom. Un grelot sonne. Adam passe à Tom. Tour. Espace du jeu. Tom passe. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2586,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2753,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. La lumière est claire. On s'assoit un moment. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. Le tapis était l'espace du jeu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2920,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3087,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Des miettes dorment sur la table. On respire, un, deux. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. Le ballon est rangé. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Papa serre Adam tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3254,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3421,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Un chat miaule une fois. On referme le sac. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. On a attendu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3588,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3755,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers Léa. Ça sent le pain tiède. Adam passe à Léa. Léa attend, puis passe. Espace du jeu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3946,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3875,7 +3975,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Voilà le matin. Les chaussures font toc toc. On essuie une miette. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. On a dit merci. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Adam range. Papa dit : c'est bien.</t>
+          <t>Voilà le matin. Les chaussures font toc toc. On essuie une miette. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. On a dit merci. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Adam range. C'est bien.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4013,6 +4113,12 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. Les chaussures font toc toc. On essuie une miette. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. On a dit merci. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Adam range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4281,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4448,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. La couverture est douce. On met le doudou près. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. Le tapis était l'espace du jeu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. On souffle. Adam sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4615,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4661,6 +4782,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Une cloche tinte au loin. On lace les chaussures. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. Le ballon est rangé. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Adam prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4949,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5116,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers Sami. Un rire court, tout petit. Adam passe à Sami. Sami reste sur le tapis. Tour. Passer. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5307,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5474,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. Le bois sent le chaud. On met le manteau. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. On a attendu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5641,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5808,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Une goutte tombe, ploc. On boit une gorgée. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. On a dit merci. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Papa serre Adam tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5975,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6142,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Le savon sent la fleur. On feuillette le livre. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. Le tapis était l'espace du jeu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6309,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6305,6 +6476,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose le bus. Le ballon revient. Adam attend son tour. Puis Adam passe. Espace du jeu, le tapis. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6481,6 +6657,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Avant de recevoir, on fait quoi ?</t>
         </is>
       </c>
     </row>
@@ -6649,6 +6830,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Chacun a un tour. Adam a attendu. Puis passer. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6837,6 +7023,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7001,6 +7192,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers Tom. Ça sent le pain tiède. Tom dit merci. Adam attend son tour. Espace du jeu. Passer. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7187,6 +7383,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7211,7 +7412,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Voilà le matin. Le tissu est tout doux. On referme le livre. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. Le ballon est rangé. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Adam range. Papa dit : c'est bien.</t>
+          <t>Voilà le matin. Le tissu est tout doux. On referme le livre. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. Le ballon est rangé. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Adam range. C'est bien.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7349,6 +7550,12 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. Le tissu est tout doux. On referme le livre. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. Le ballon est rangé. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Adam range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7511,6 +7718,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7673,6 +7885,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Une cuillère tinte. On pose le ballon. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. On a attendu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. On souffle. Adam sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7835,6 +8052,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7997,6 +8219,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Le sable est tiède. On secoue le sable. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. On a dit merci. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Adam prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8159,6 +8386,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8321,6 +8553,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers Léa. La fenêtre vibre un peu. Léa rit. Le ballon reste dans l'espace du jeu. Tour. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8507,6 +8744,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8669,6 +8911,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. Un rire court, tout petit. On caresse le tissu. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. Le tapis était l'espace du jeu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8831,6 +9078,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8993,6 +9245,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Le papier froisse, chut. On tend la main. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. Le ballon est rangé. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Papa serre Adam tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9155,6 +9412,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9317,6 +9579,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. L'herbe chatouille le mollet. On chante un petit air. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. On a attendu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9479,6 +9746,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9641,6 +9913,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers Sami. Le savon mousse entre les doigts. Sami s'assoit. Adam passe. Tour. Espace du jeu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9827,6 +10104,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9851,7 +10133,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Voilà le matin. Un pigeon roucoule. On compte jusqu'à trois. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. On a dit merci. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Adam range. Papa dit : c'est bien.</t>
+          <t>Voilà le matin. Un pigeon roucoule. On compte jusqu'à trois. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. On a dit merci. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Adam range. C'est bien.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -9989,6 +10271,12 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. Un pigeon roucoule. On compte jusqu'à trois. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. On a dit merci. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Adam range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10151,6 +10439,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10313,6 +10606,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. La fenêtre vibre un peu. On montre du doigt. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. Le tapis était l'espace du jeu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. On souffle. Adam sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10475,6 +10773,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10637,6 +10940,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Le lait est froid dans le verre. On range la chaise. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. Le ballon est rangé. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Adam prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10799,6 +11107,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10961,6 +11274,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose la voiture. Papa montre le bord du tapis. Espace du jeu. On passe le ballon. Chacun a un tour. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11137,6 +11455,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On reste où avec le ballon ?</t>
         </is>
       </c>
     </row>
@@ -11305,6 +11628,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Le ballon est resté dans l'espace du jeu. Passer. Tour. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11493,6 +11821,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -11657,6 +11990,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers Tom. La laine gratte un peu. Tom tend les mains. Adam passe. Espace du jeu. Tour. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11843,6 +12181,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12005,6 +12348,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. La corde du sac est rêche. On range un objet. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. On a attendu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12167,6 +12515,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12329,6 +12682,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Le savon mousse entre les doigts. On se tient la main. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. On a dit merci. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Papa serre Adam tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12491,6 +12849,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12653,6 +13016,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Un ruisseau chante. On dit merci. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. Le tapis était l'espace du jeu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12815,6 +13183,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12977,6 +13350,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers Léa. Un nuage passe lentement. Léa pose un pied sur le tapis. Espace du jeu. On passe. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13163,6 +13541,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13187,7 +13570,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Voilà le matin. La laine gratte un peu. On souffle doucement. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. Le ballon est rangé. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Adam range. Papa dit : c'est bien.</t>
+          <t>Voilà le matin. La laine gratte un peu. On souffle doucement. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. Le ballon est rangé. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Adam range. C'est bien.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13325,6 +13708,12 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. La laine gratte un peu. On souffle doucement. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. Le ballon est rangé. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Adam range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13487,6 +13876,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13649,6 +14043,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Un pain croustille. On écoute jusqu'au bout. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. On a attendu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. On souffle. Adam sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13811,6 +14210,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13973,6 +14377,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Le savon glisse. On attend son tour. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. On a dit merci. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Adam prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14135,6 +14544,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14297,6 +14711,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers Sami. Un nuage passe lentement. Sami rend le ballon. Tour. Passer. Espace du jeu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14483,6 +14902,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14645,6 +15069,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. Une plume vole. On sourit ensemble. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. Le tapis était l'espace du jeu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Adam dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14807,6 +15236,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14969,6 +15403,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Le banc est lisse. On pose les pieds par terre. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. Le ballon est rangé. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Papa serre Adam tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15131,6 +15570,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15293,6 +15737,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Un grelot sonne. On parle tout bas. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. On a attendu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15455,6 +15904,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15473,7 +15927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15504,6 +15958,13 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-JEU-001.xlsx
+++ b/stories/arbres/TREE-JEU-001.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Adam passe le ballon à papa. Papa attend, puis passe. Tour. Espace du jeu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1516,6 +1522,7 @@
           <t>narrateur|On peut prendre le train, le bus, ou la voiture.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1684,6 +1691,7 @@
 papa|On passe, on attend. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1867,6 +1875,7 @@
           <t>narrateur|Le ballon, on le fait quoi ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2038,6 +2047,7 @@
           <t>narrateur|Adam a passé le ballon. Tour. Espace du jeu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2233,6 +2243,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2400,6 +2411,7 @@
           <t>narrateur|Adam va vers Tom. Un grelot sonne. Adam passe à Tom. Tour. Espace du jeu. Tom passe. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2591,6 +2603,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2758,6 +2771,7 @@
           <t>narrateur|Voilà le matin. La lumière est claire. On s'assoit un moment. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. Le tapis était l'espace du jeu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2925,6 +2939,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3092,6 +3107,7 @@
           <t>narrateur|Voilà après la sieste. Des miettes dorment sur la table. On respire, un, deux. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. Le ballon est rangé. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Papa serre Adam tout doux.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3259,6 +3275,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3426,6 +3443,7 @@
           <t>narrateur|Voilà le soir. Un chat miaule une fois. On referme le sac. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. On a attendu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3593,6 +3611,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3760,6 +3779,7 @@
           <t>narrateur|Adam va vers Léa. Ça sent le pain tiède. Adam passe à Léa. Léa attend, puis passe. Espace du jeu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3951,6 +3971,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4119,6 +4140,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4286,6 +4308,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4453,6 +4476,7 @@
           <t>narrateur|Voilà après la sieste. La couverture est douce. On met le doudou près. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. Le tapis était l'espace du jeu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. On souffle. Adam sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4620,6 +4644,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4787,6 +4812,7 @@
           <t>narrateur|Voilà le soir. Une cloche tinte au loin. On lace les chaussures. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. Le ballon est rangé. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Adam prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4954,6 +4980,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5121,6 +5148,7 @@
           <t>narrateur|Adam va vers Sami. Un rire court, tout petit. Adam passe à Sami. Sami reste sur le tapis. Tour. Passer. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5312,6 +5340,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5479,6 +5508,7 @@
           <t>narrateur|Voilà le matin. Le bois sent le chaud. On met le manteau. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. On a attendu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5646,6 +5676,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5813,6 +5844,7 @@
           <t>narrateur|Voilà après la sieste. Une goutte tombe, ploc. On boit une gorgée. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. On a dit merci. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Papa serre Adam tout doux.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5980,6 +6012,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6147,6 +6180,7 @@
           <t>narrateur|Voilà le soir. Le savon sent la fleur. On feuillette le livre. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. Le tapis était l'espace du jeu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6314,6 +6348,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6481,6 +6516,7 @@
           <t>narrateur|Adam pose le bus. Le ballon revient. Adam attend son tour. Puis Adam passe. Espace du jeu, le tapis. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6664,6 +6700,7 @@
           <t>narrateur|Avant de recevoir, on fait quoi ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6835,6 +6872,7 @@
           <t>narrateur|Chacun a un tour. Adam a attendu. Puis passer. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7030,6 +7068,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7197,6 +7236,7 @@
           <t>narrateur|Adam va vers Tom. Ça sent le pain tiède. Tom dit merci. Adam attend son tour. Espace du jeu. Passer. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7388,6 +7428,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7556,6 +7597,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7723,6 +7765,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7890,6 +7933,7 @@
           <t>narrateur|Voilà après la sieste. Une cuillère tinte. On pose le ballon. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. On a attendu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. On souffle. Adam sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8057,6 +8101,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8224,6 +8269,7 @@
           <t>narrateur|Voilà le soir. Le sable est tiède. On secoue le sable. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. On a dit merci. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Adam prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8391,6 +8437,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8558,6 +8605,7 @@
           <t>narrateur|Adam va vers Léa. La fenêtre vibre un peu. Léa rit. Le ballon reste dans l'espace du jeu. Tour. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8749,6 +8797,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8916,6 +8965,7 @@
           <t>narrateur|Voilà le matin. Un rire court, tout petit. On caresse le tissu. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. Le tapis était l'espace du jeu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9083,6 +9133,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9250,6 +9301,7 @@
           <t>narrateur|Voilà après la sieste. Le papier froisse, chut. On tend la main. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. Le ballon est rangé. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Papa serre Adam tout doux.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9417,6 +9469,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9584,6 +9637,7 @@
           <t>narrateur|Voilà le soir. L'herbe chatouille le mollet. On chante un petit air. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. On a attendu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9751,6 +9805,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9918,6 +9973,7 @@
           <t>narrateur|Adam va vers Sami. Le savon mousse entre les doigts. Sami s'assoit. Adam passe. Tour. Espace du jeu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10109,6 +10165,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10277,6 +10334,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10444,6 +10502,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10611,6 +10670,7 @@
           <t>narrateur|Voilà après la sieste. La fenêtre vibre un peu. On montre du doigt. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. Le tapis était l'espace du jeu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. On souffle. Adam sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10778,6 +10838,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10945,6 +11006,7 @@
           <t>narrateur|Voilà le soir. Le lait est froid dans le verre. On range la chaise. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. Le ballon est rangé. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Adam prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11112,6 +11174,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11279,6 +11342,7 @@
           <t>narrateur|Adam pose la voiture. Papa montre le bord du tapis. Espace du jeu. On passe le ballon. Chacun a un tour. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11462,6 +11526,7 @@
           <t>narrateur|On reste où avec le ballon ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11633,6 +11698,7 @@
           <t>narrateur|Le ballon est resté dans l'espace du jeu. Passer. Tour. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11828,6 +11894,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11995,6 +12062,7 @@
           <t>narrateur|Adam va vers Tom. La laine gratte un peu. Tom tend les mains. Adam passe. Espace du jeu. Tour. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12186,6 +12254,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12353,6 +12422,7 @@
           <t>narrateur|Voilà le matin. La corde du sac est rêche. On range un objet. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. On a attendu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12520,6 +12590,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12687,6 +12758,7 @@
           <t>narrateur|Voilà après la sieste. Le savon mousse entre les doigts. On se tient la main. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. On a dit merci. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Papa serre Adam tout doux.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12854,6 +12926,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13021,6 +13094,7 @@
           <t>narrateur|Voilà le soir. Un ruisseau chante. On dit merci. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. Le tapis était l'espace du jeu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13188,6 +13262,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13355,6 +13430,7 @@
           <t>narrateur|Adam va vers Léa. Un nuage passe lentement. Léa pose un pied sur le tapis. Espace du jeu. On passe. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13546,6 +13622,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13714,6 +13791,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13881,6 +13959,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14048,6 +14127,7 @@
           <t>narrateur|Voilà après la sieste. Un pain croustille. On écoute jusqu'au bout. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. On a attendu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. On souffle. Adam sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14215,6 +14295,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14382,6 +14463,7 @@
           <t>narrateur|Voilà le soir. Le savon glisse. On attend son tour. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. On a dit merci. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Adam prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14549,6 +14631,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14716,6 +14799,7 @@
           <t>narrateur|Adam va vers Sami. Un nuage passe lentement. Sami rend le ballon. Tour. Passer. Espace du jeu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14907,6 +14991,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15074,6 +15159,7 @@
           <t>narrateur|Voilà le matin. Une plume vole. On sourit ensemble. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. Le tapis était l'espace du jeu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Adam dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15241,6 +15327,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15408,6 +15495,7 @@
           <t>narrateur|Voilà après la sieste. Le banc est lisse. On pose les pieds par terre. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. Le ballon est rangé. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Papa serre Adam tout doux.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15575,6 +15663,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15742,6 +15831,7 @@
           <t>narrateur|Voilà le soir. Un grelot sonne. On parle tout bas. On s'est passé le ballon. Chacun a eu un tour. Dans l'espace du jeu. On a attendu. On se passe le ballon. Chacun a un tour. On reste dans l'espace du jeu. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15909,6 +15999,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15927,7 +16018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15965,6 +16056,20 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15979,7 +16084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16166,6 +16271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
